--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504516</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504513</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504510</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504517</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504519</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504522</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504846</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504847</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504849</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504850</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504851</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504852</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504515</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504521</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,8 +3136,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504848</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504516</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504507</v>
       </c>
       <c r="B4" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504513</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504505</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504506</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504510</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504511</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504512</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504517</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504519</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504522</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504846</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135504847</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135504849</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135504850</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135504851</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135504852</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135504508</v>
       </c>
       <c r="B20" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135504515</v>
       </c>
       <c r="B21" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135504521</v>
       </c>
       <c r="B22" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135504518</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504848</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504516</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504507</v>
       </c>
       <c r="B4" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504513</v>
       </c>
       <c r="B5" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504505</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504506</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504510</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504511</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504512</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504517</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504519</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504522</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504846</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135504847</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135504849</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135504850</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135504851</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135504852</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135504508</v>
       </c>
       <c r="B20" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135504515</v>
       </c>
       <c r="B21" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135504521</v>
       </c>
       <c r="B22" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135504518</v>
       </c>
       <c r="B23" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135504516</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504513</v>
       </c>
       <c r="B5" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135504518</v>
       </c>
       <c r="B23" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504848</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504516</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504507</v>
       </c>
       <c r="B4" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504513</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504505</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504506</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504510</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504511</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504512</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504517</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504519</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504522</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504846</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135504847</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135504849</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135504850</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135504851</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135504852</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135504508</v>
       </c>
       <c r="B20" t="n">
-        <v>83411</v>
+        <v>83413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135504515</v>
       </c>
       <c r="B21" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135504521</v>
       </c>
       <c r="B22" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135504518</v>
       </c>
       <c r="B23" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30084-2025 artfynd.xlsx
+++ b/artfynd/A 30084-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504848</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504516</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504507</v>
       </c>
       <c r="B4" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504513</v>
       </c>
       <c r="B5" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504505</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504506</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504510</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504511</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504512</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504517</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504519</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504522</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504846</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135504847</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135504849</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135504850</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135504851</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135504852</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135504508</v>
       </c>
       <c r="B20" t="n">
-        <v>83413</v>
+        <v>83414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135504515</v>
       </c>
       <c r="B21" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135504521</v>
       </c>
       <c r="B22" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135504518</v>
       </c>
       <c r="B23" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
